--- a/Reports/FIO/CertificateToCourt/CertificateToCourt.xlsx
+++ b/Reports/FIO/CertificateToCourt/CertificateToCourt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\CertificateToCourt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8794C0-7290-4E98-92C6-1984355DA0BC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2789EB-EEA2-456E-8C38-12E9A168B374}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,10 +102,10 @@
     <t>"в том, что он (она) действительно зарегистрирован(а) в  ".$this-&gt;H['pref_region']." " .$this-&gt;H['name_region']</t>
   </si>
   <si>
-    <t>Информация не является исчерпывающей, в связи с всиуплением в силу приказа МВД России</t>
-  </si>
-  <si>
     <t>№984 от  31.12.2017 г.</t>
+  </si>
+  <si>
+    <t>Информация не является исчерпывающей, в связи с вступлением в силу приказа МВД России</t>
   </si>
 </sst>
 </file>
@@ -912,7 +912,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="6"/>
@@ -923,7 +923,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="6"/>
